--- a/outputs/data_cleaning_log.xlsx
+++ b/outputs/data_cleaning_log.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ariel\Documents\case study\wellness company\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ariel\Documents\GitHub\Market-Analysis-for-Bellabeat-s-Smart-Device\outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D56E29EE-B077-4AAE-86CE-B0115CA4F83D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{078B0C1C-D3C1-471E-8673-16A8FE9C9970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22180" windowHeight="14140" activeTab="1" xr2:uid="{D8861D8A-FF46-4402-AA02-7363FD0377A3}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22180" windowHeight="14140" xr2:uid="{D8861D8A-FF46-4402-AA02-7363FD0377A3}"/>
   </bookViews>
   <sheets>
     <sheet name="checklist" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2008" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2027" uniqueCount="72">
   <si>
     <t>cleaning stage</t>
   </si>
@@ -253,6 +253,12 @@
   <si>
     <t>Ariel</t>
   </si>
+  <si>
+    <t>multiple</t>
+  </si>
+  <si>
+    <t>Incorrect data type, nullable, no primary Key</t>
+  </si>
 </sst>
 </file>
 
@@ -316,7 +322,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -340,11 +346,35 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="5">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -363,24 +393,6 @@
         <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -453,6 +465,7 @@
     <filterColumn colId="0">
       <filters>
         <filter val="dailyactivity_mergerd_3"/>
+        <filter val="dailyactivity_mergerd_4"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -467,10 +480,10 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DDE942B3-4ED8-4944-9096-1F7E6149D97E}" name="Table2" displayName="Table2" ref="A1:D29" totalsRowShown="0" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DDE942B3-4ED8-4944-9096-1F7E6149D97E}" name="Table2" displayName="Table2" ref="A1:D29" totalsRowShown="0" headerRowDxfId="1">
   <autoFilter ref="A1:D29" xr:uid="{DDE942B3-4ED8-4944-9096-1F7E6149D97E}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{D7E221F1-D425-4099-92C7-D76B513504F0}" name="dataset" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{D7E221F1-D425-4099-92C7-D76B513504F0}" name="dataset" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{50655C6A-4481-427D-BD22-66F400EAB4DF}" name="metric"/>
     <tableColumn id="3" xr3:uid="{AA5E460B-8849-4E63-BC3E-54131DED3750}" name="value_before"/>
     <tableColumn id="4" xr3:uid="{802186CB-FABD-47F3-9026-E57DB5B087B5}" name="value_after"/>
@@ -847,7 +860,7 @@
         <v>5</v>
       </c>
       <c r="D3" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" s="7"/>
     </row>
@@ -862,7 +875,7 @@
         <v>6</v>
       </c>
       <c r="D4" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="7"/>
     </row>
@@ -967,7 +980,7 @@
         <v>13</v>
       </c>
       <c r="D11" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="7"/>
     </row>
@@ -1166,7 +1179,7 @@
       </c>
       <c r="E24" s="7"/>
     </row>
-    <row r="25" spans="1:5" ht="16" hidden="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:5" ht="16" x14ac:dyDescent="0.4">
       <c r="A25" s="7" t="s">
         <v>42</v>
       </c>
@@ -1177,11 +1190,11 @@
         <v>4</v>
       </c>
       <c r="D25" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" s="7"/>
     </row>
-    <row r="26" spans="1:5" ht="16" hidden="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:5" ht="16" x14ac:dyDescent="0.4">
       <c r="A26" s="7" t="s">
         <v>42</v>
       </c>
@@ -1192,11 +1205,11 @@
         <v>5</v>
       </c>
       <c r="D26" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" s="7"/>
     </row>
-    <row r="27" spans="1:5" ht="16" hidden="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:5" ht="16" x14ac:dyDescent="0.4">
       <c r="A27" s="7" t="s">
         <v>42</v>
       </c>
@@ -1207,11 +1220,11 @@
         <v>6</v>
       </c>
       <c r="D27" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" s="7"/>
     </row>
-    <row r="28" spans="1:5" ht="16" hidden="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:5" ht="16" x14ac:dyDescent="0.4">
       <c r="A28" s="7" t="s">
         <v>42</v>
       </c>
@@ -1226,7 +1239,7 @@
       </c>
       <c r="E28" s="7"/>
     </row>
-    <row r="29" spans="1:5" ht="16" hidden="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:5" ht="16" x14ac:dyDescent="0.4">
       <c r="A29" s="7" t="s">
         <v>42</v>
       </c>
@@ -1240,7 +1253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="16" hidden="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:5" ht="16" x14ac:dyDescent="0.4">
       <c r="A30" s="7" t="s">
         <v>42</v>
       </c>
@@ -1254,7 +1267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="16" hidden="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:5" ht="16" x14ac:dyDescent="0.4">
       <c r="A31" s="7" t="s">
         <v>42</v>
       </c>
@@ -1268,7 +1281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="16" hidden="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:5" ht="16" x14ac:dyDescent="0.4">
       <c r="A32" s="7" t="s">
         <v>42</v>
       </c>
@@ -1282,7 +1295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="16" hidden="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:4" ht="16" x14ac:dyDescent="0.4">
       <c r="A33" s="7" t="s">
         <v>42</v>
       </c>
@@ -1296,7 +1309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="16" hidden="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:4" ht="16" x14ac:dyDescent="0.4">
       <c r="A34" s="7" t="s">
         <v>42</v>
       </c>
@@ -1307,10 +1320,10 @@
         <v>13</v>
       </c>
       <c r="D34" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="16" hidden="1" x14ac:dyDescent="0.4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="16" x14ac:dyDescent="0.4">
       <c r="A35" s="7" t="s">
         <v>42</v>
       </c>
@@ -1324,7 +1337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="16" hidden="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:4" ht="16" x14ac:dyDescent="0.4">
       <c r="A36" s="7" t="s">
         <v>42</v>
       </c>
@@ -1338,7 +1351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="16" hidden="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:4" ht="16" x14ac:dyDescent="0.4">
       <c r="A37" s="7" t="s">
         <v>42</v>
       </c>
@@ -1352,7 +1365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="16" hidden="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:4" ht="16" x14ac:dyDescent="0.4">
       <c r="A38" s="7" t="s">
         <v>42</v>
       </c>
@@ -1366,7 +1379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="16" hidden="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:4" ht="16" x14ac:dyDescent="0.4">
       <c r="A39" s="7" t="s">
         <v>42</v>
       </c>
@@ -1380,7 +1393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="16" hidden="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:4" ht="16" x14ac:dyDescent="0.4">
       <c r="A40" s="7" t="s">
         <v>42</v>
       </c>
@@ -1394,7 +1407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="16" hidden="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:4" ht="16" x14ac:dyDescent="0.4">
       <c r="A41" s="7" t="s">
         <v>42</v>
       </c>
@@ -1408,7 +1421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="16" hidden="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:4" ht="16" x14ac:dyDescent="0.4">
       <c r="A42" s="7" t="s">
         <v>42</v>
       </c>
@@ -1422,7 +1435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="16" hidden="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:4" ht="16" x14ac:dyDescent="0.4">
       <c r="A43" s="7" t="s">
         <v>42</v>
       </c>
@@ -1436,7 +1449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="16" hidden="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:4" ht="16" x14ac:dyDescent="0.4">
       <c r="A44" s="7" t="s">
         <v>42</v>
       </c>
@@ -1450,7 +1463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="16" hidden="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:4" ht="16" x14ac:dyDescent="0.4">
       <c r="A45" s="7" t="s">
         <v>42</v>
       </c>
@@ -1464,7 +1477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="16" hidden="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:4" ht="16" x14ac:dyDescent="0.4">
       <c r="A46" s="7" t="s">
         <v>42</v>
       </c>
@@ -1478,7 +1491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="16" hidden="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:4" ht="16" x14ac:dyDescent="0.4">
       <c r="A47" s="7" t="s">
         <v>42</v>
       </c>
@@ -9875,14 +9888,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBA96DDF-F8FB-441F-AFE6-9B57EF03C5AF}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.90625" customWidth="1"/>
+    <col min="1" max="1" width="12.90625" style="4" customWidth="1"/>
     <col min="2" max="2" width="32.54296875" style="4" customWidth="1"/>
-    <col min="3" max="3" width="17.7265625" style="4" customWidth="1"/>
-    <col min="4" max="4" width="19.36328125" style="4" customWidth="1"/>
-    <col min="5" max="5" width="14.36328125" style="4" customWidth="1"/>
+    <col min="3" max="3" width="17.7265625" style="9" customWidth="1"/>
+    <col min="4" max="4" width="49.54296875" style="4" customWidth="1"/>
+    <col min="5" max="5" width="47.54296875" style="4" customWidth="1"/>
     <col min="6" max="6" width="15.81640625" style="4" customWidth="1"/>
     <col min="7" max="7" width="24.26953125" style="4" customWidth="1"/>
     <col min="8" max="8" width="20.36328125" style="4" customWidth="1"/>
@@ -9898,7 +9911,7 @@
       <c r="B1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="8" t="s">
         <v>30</v>
       </c>
       <c r="D1" s="3" t="s">
@@ -9925,16 +9938,105 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="6">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>41</v>
       </c>
+      <c r="C2" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="J2" s="4" t="s">
         <v>69</v>
       </c>
     </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A3" s="6">
+        <v>46196</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="J4" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="J5" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="J6" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="J7" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="J8" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="J9" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="J10" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="J11" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="J12" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="J13" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="J14" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="J15" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="J16" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/outputs/data_cleaning_log.xlsx
+++ b/outputs/data_cleaning_log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ariel\Documents\GitHub\Market-Analysis-for-Bellabeat-s-Smart-Device\outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{078B0C1C-D3C1-471E-8673-16A8FE9C9970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69C608CF-DD15-46AC-AD8D-499F230CFC05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22180" windowHeight="14140" xr2:uid="{D8861D8A-FF46-4402-AA02-7363FD0377A3}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2027" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2059" uniqueCount="89">
   <si>
     <t>cleaning stage</t>
   </si>
@@ -254,10 +254,61 @@
     <t>Ariel</t>
   </si>
   <si>
-    <t>multiple</t>
+    <t>ActivityDate</t>
   </si>
   <si>
-    <t>Incorrect data type, nullable, no primary Key</t>
+    <t>Incorrect data type</t>
+  </si>
+  <si>
+    <t>Converted TEXT to DATE using STR_TO-DATE</t>
+  </si>
+  <si>
+    <t>steps, minutes.etc</t>
+  </si>
+  <si>
+    <t>%m/%d/%Y' - DATE format (YYYY-MM-DD)</t>
+  </si>
+  <si>
+    <t>double - INT</t>
+  </si>
+  <si>
+    <t>Converted DOUBLE to INT using MODIFY</t>
+  </si>
+  <si>
+    <t>calories distance.etc</t>
+  </si>
+  <si>
+    <t>Converted DOUBLE to DECIMAL(10,2) using MODIFY</t>
+  </si>
+  <si>
+    <t>double - DECIMAL(10,2)</t>
+  </si>
+  <si>
+    <t>Converted TEXT to DATE using MODIFY</t>
+  </si>
+  <si>
+    <t>TEXT - DATE</t>
+  </si>
+  <si>
+    <t>3/25/2016</t>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>extra 2 Id</t>
+  </si>
+  <si>
+    <t>select from... where not in</t>
+  </si>
+  <si>
+    <t>keep them</t>
+  </si>
+  <si>
+    <t>2891001357, 6391747486</t>
+  </si>
+  <si>
+    <t>2891001357', '6391747486</t>
   </si>
 </sst>
 </file>
@@ -322,7 +373,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -352,11 +403,69 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="17">
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -471,19 +580,38 @@
   </autoFilter>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{E53E5277-173A-4585-81BD-A0BF1047A7AC}" name="dataset"/>
-    <tableColumn id="2" xr3:uid="{E528ECEF-F174-4AB1-952A-696E5137C6B6}" name="cleaning stage" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{64837233-1578-409C-BF0B-E59D82D5C557}" name="description" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{800E6762-7BE8-4E53-840B-9CB6F5CA121F}" name="status" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{E528ECEF-F174-4AB1-952A-696E5137C6B6}" name="cleaning stage" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{64837233-1578-409C-BF0B-E59D82D5C557}" name="description" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{800E6762-7BE8-4E53-840B-9CB6F5CA121F}" name="status" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DDE942B3-4ED8-4944-9096-1F7E6149D97E}" name="Table2" displayName="Table2" ref="A1:D29" totalsRowShown="0" headerRowDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{34C212A9-CBB2-4619-AEE7-A786A8932D6D}" name="Table3" displayName="Table3" ref="A1:J16" totalsRowShown="0" headerRowDxfId="6" dataDxfId="7">
+  <autoFilter ref="A1:J16" xr:uid="{34C212A9-CBB2-4619-AEE7-A786A8932D6D}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{06066BF7-5B9D-46E9-84FA-309C8E89AE6C}" name="date" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{CD897D74-DB13-4FFC-A31B-0F4C4B0C5B6E}" name="dataset" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{E7465859-8768-49F0-842D-346C718DE76B}" name="column" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{680EB9A4-4FC9-4F8B-9051-A63F3353E929}" name="issue_type" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{5B627470-7B0E-4CDF-9678-91C89BABE0E0}" name="action" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{6D5EFBCA-68A2-4716-8763-7DCBFB3D0FD1}" name="rule" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{D0B1A33C-99A9-4013-8B6B-ACA4747C4DD6}" name="before_sample" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{99DAC789-431A-4385-AFFD-8C1F2433BC9E}" name="after_sample" dataDxfId="0"/>
+    <tableColumn id="9" xr3:uid="{2C3B6F91-819A-4D40-888D-91B2F03847E0}" name="affected_rows" dataDxfId="1"/>
+    <tableColumn id="10" xr3:uid="{D5525D7E-6701-41F6-8F05-0A0D1E90EF77}" name="owner" dataDxfId="8"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DDE942B3-4ED8-4944-9096-1F7E6149D97E}" name="Table2" displayName="Table2" ref="A1:D29" totalsRowShown="0" headerRowDxfId="13">
   <autoFilter ref="A1:D29" xr:uid="{DDE942B3-4ED8-4944-9096-1F7E6149D97E}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{D7E221F1-D425-4099-92C7-D76B513504F0}" name="dataset" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{D7E221F1-D425-4099-92C7-D76B513504F0}" name="dataset" dataDxfId="12"/>
     <tableColumn id="2" xr3:uid="{50655C6A-4481-427D-BD22-66F400EAB4DF}" name="metric"/>
     <tableColumn id="3" xr3:uid="{AA5E460B-8849-4E63-BC3E-54131DED3750}" name="value_before"/>
     <tableColumn id="4" xr3:uid="{802186CB-FABD-47F3-9026-E57DB5B087B5}" name="value_after"/>
@@ -890,7 +1018,7 @@
         <v>7</v>
       </c>
       <c r="D5" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="7"/>
     </row>
@@ -905,7 +1033,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="7"/>
     </row>
@@ -920,7 +1048,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" s="7"/>
     </row>
@@ -935,7 +1063,7 @@
         <v>10</v>
       </c>
       <c r="D8" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="7"/>
     </row>
@@ -950,7 +1078,7 @@
         <v>11</v>
       </c>
       <c r="D9" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="7"/>
     </row>
@@ -980,7 +1108,7 @@
         <v>13</v>
       </c>
       <c r="D11" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" s="7"/>
     </row>
@@ -995,7 +1123,7 @@
         <v>14</v>
       </c>
       <c r="D12" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="7"/>
     </row>
@@ -1010,7 +1138,7 @@
         <v>15</v>
       </c>
       <c r="D13" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" s="7"/>
     </row>
@@ -1235,7 +1363,7 @@
         <v>7</v>
       </c>
       <c r="D28" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" s="7"/>
     </row>
@@ -1250,7 +1378,7 @@
         <v>8</v>
       </c>
       <c r="D29" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="16" x14ac:dyDescent="0.4">
@@ -1264,7 +1392,7 @@
         <v>9</v>
       </c>
       <c r="D30" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="16" x14ac:dyDescent="0.4">
@@ -1278,7 +1406,7 @@
         <v>10</v>
       </c>
       <c r="D31" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="16" x14ac:dyDescent="0.4">
@@ -1292,7 +1420,7 @@
         <v>11</v>
       </c>
       <c r="D32" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="16" x14ac:dyDescent="0.4">
@@ -1320,7 +1448,7 @@
         <v>13</v>
       </c>
       <c r="D34" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="16" x14ac:dyDescent="0.4">
@@ -1334,7 +1462,7 @@
         <v>14</v>
       </c>
       <c r="D35" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="16" x14ac:dyDescent="0.4">
@@ -1348,7 +1476,7 @@
         <v>15</v>
       </c>
       <c r="D36" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="16" x14ac:dyDescent="0.4">
@@ -9892,14 +10020,14 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.90625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="32.54296875" style="4" customWidth="1"/>
+    <col min="2" max="2" width="27.90625" style="4" customWidth="1"/>
     <col min="3" max="3" width="17.7265625" style="9" customWidth="1"/>
-    <col min="4" max="4" width="49.54296875" style="4" customWidth="1"/>
-    <col min="5" max="5" width="47.54296875" style="4" customWidth="1"/>
-    <col min="6" max="6" width="15.81640625" style="4" customWidth="1"/>
-    <col min="7" max="7" width="24.26953125" style="4" customWidth="1"/>
-    <col min="8" max="8" width="20.36328125" style="4" customWidth="1"/>
-    <col min="9" max="9" width="15.1796875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="37.6328125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="29.08984375" style="9" customWidth="1"/>
+    <col min="6" max="6" width="31.08984375" style="9" customWidth="1"/>
+    <col min="7" max="7" width="15" style="9" customWidth="1"/>
+    <col min="8" max="8" width="14.36328125" style="9" customWidth="1"/>
+    <col min="9" max="9" width="19.36328125" style="4" customWidth="1"/>
     <col min="10" max="10" width="8.7265625" style="4"/>
     <col min="11" max="11" width="11.36328125" style="4" customWidth="1"/>
   </cols>
@@ -9917,16 +10045,16 @@
       <c r="D1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="8" t="s">
         <v>35</v>
       </c>
       <c r="I1" s="3" t="s">
@@ -9936,12 +10064,12 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="6">
-        <v>46196</v>
+        <v>46198</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>70</v>
@@ -9949,88 +10077,277 @@
       <c r="D2" s="4" t="s">
         <v>71</v>
       </c>
+      <c r="E2" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="G2" s="11">
+        <v>42708</v>
+      </c>
+      <c r="H2" s="11">
+        <v>42472</v>
+      </c>
+      <c r="I2" s="4">
+        <v>940</v>
+      </c>
       <c r="J2" s="4" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="6">
-        <v>46196</v>
+        <v>46198</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>71</v>
       </c>
+      <c r="E3" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="G3" s="9">
+        <v>9117</v>
+      </c>
+      <c r="H3" s="9">
+        <v>9117</v>
+      </c>
+      <c r="I3" s="4">
+        <v>940</v>
+      </c>
       <c r="J3" s="4" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A4" s="6">
+        <v>46198</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="G4" s="9">
+        <v>6.9699997901916504</v>
+      </c>
+      <c r="H4" s="9">
+        <v>6.97</v>
+      </c>
+      <c r="I4" s="4">
+        <v>940</v>
+      </c>
       <c r="J4" s="4" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A5" s="6">
+        <v>46198</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="H5" s="11">
+        <v>42454</v>
+      </c>
+      <c r="I5" s="4">
+        <v>457</v>
+      </c>
       <c r="J5" s="4" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A6" s="6">
+        <v>46198</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="G6" s="9">
+        <v>33</v>
+      </c>
+      <c r="H6" s="9">
+        <v>33</v>
+      </c>
+      <c r="I6" s="4">
+        <v>457</v>
+      </c>
       <c r="J6" s="4" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A7" s="6">
+        <v>46198</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="G7" s="9">
+        <v>7.1100001335143999</v>
+      </c>
+      <c r="H7" s="9">
+        <v>7.11</v>
+      </c>
+      <c r="I7" s="4">
+        <v>457</v>
+      </c>
       <c r="J7" s="4" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A8" s="6">
+        <v>46198</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0</v>
+      </c>
       <c r="J8" s="4" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A9" s="6">
+        <v>46198</v>
+      </c>
       <c r="J9" s="4" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10" s="6">
+        <v>46198</v>
+      </c>
       <c r="J10" s="4" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A11" s="6">
+        <v>46198</v>
+      </c>
       <c r="J11" s="4" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A12" s="6">
+        <v>46198</v>
+      </c>
       <c r="J12" s="4" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13" s="6">
+        <v>46198</v>
+      </c>
       <c r="J13" s="4" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A14" s="6">
+        <v>46198</v>
+      </c>
       <c r="J14" s="4" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A15" s="6">
+        <v>46198</v>
+      </c>
       <c r="J15" s="4" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A16" s="6">
+        <v>46198</v>
+      </c>
       <c r="J16" s="4" t="s">
         <v>69</v>
       </c>
@@ -10038,6 +10355,9 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
